--- a/artfynd/A 60502-2024 artfynd.xlsx
+++ b/artfynd/A 60502-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>3393291</v>
       </c>
       <c r="B2" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515439.9228169039</v>
+        <v>515440</v>
       </c>
       <c r="R2" t="n">
-        <v>6242802.441440366</v>
+        <v>6242802</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2012-06-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-06-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4712135</v>
+        <v>4433761</v>
       </c>
       <c r="B3" t="n">
-        <v>96926</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222295</v>
+        <v>222133</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515369.5551367595</v>
+        <v>515440</v>
       </c>
       <c r="R3" t="n">
-        <v>6242752.850471699</v>
+        <v>6242802</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,19 +850,9 @@
           <t>2012-06-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-06-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6260307</v>
+        <v>4712135</v>
       </c>
       <c r="B4" t="n">
-        <v>101692</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,19 +900,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224416</v>
+        <v>222295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515439.9228169039</v>
+        <v>515370</v>
       </c>
       <c r="R4" t="n">
-        <v>6242802.441440366</v>
+        <v>6242753</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,19 +957,9 @@
           <t>2012-06-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-06-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1037,58 +996,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6339345</v>
+        <v>6260307</v>
       </c>
       <c r="B5" t="n">
-        <v>98539</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>104641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224913</v>
+        <v>224416</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+          <t>Helianthemum nummularium subsp. nummularium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skärvgöl, Toratorpet, Bl</t>
+          <t>Skärvgöl Toratorpet, Bl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515439.9228169039</v>
+        <v>515440</v>
       </c>
       <c r="R5" t="n">
-        <v>6242802.441440366</v>
+        <v>6242802</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,34 +1055,19 @@
           <t>Backaryd</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>K-Ron-0748</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>2012-06-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-06-20</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>medrapportör Gunnar Olsson</t>
+          <t>Även Gunnar Ohlsson</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,21 +1081,138 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>torrbacke, tidigare betad</t>
+          <t>Torrbackar</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Bengt Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bengt Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6339345</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101348</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>224913</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig backsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skärvgöl, Toratorpet, Bl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>515440</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6242802</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Backaryd</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>K-Ron-0748</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2012-06-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2012-06-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>medrapportör Gunnar Olsson</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>torrbacke, tidigare betad</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>K-län Floraväktarna</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Bengt Nilsson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
